--- a/output/pdf_financials_xlsx/LITT.xlsx
+++ b/output/pdf_financials_xlsx/LITT.xlsx
@@ -5950,28 +5950,28 @@
         <v>1.098362</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.098362</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.182569</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.205754</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.208208</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.208208</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.208208</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.208208</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.208208</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -6341,7 +6341,7 @@
         <v>-2.662103</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>0.342497</v>
+        <v>-0.342497</v>
       </c>
       <c r="Q99" s="3" t="n">
         <v>-1.770476</v>
@@ -16198,7 +16198,11 @@
           <t>Share-based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -17513,7 +17517,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -21453,7 +21461,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -22721,7 +22733,7 @@
         <v>-2.662103</v>
       </c>
       <c r="S144" s="5" t="n">
-        <v>0.342497</v>
+        <v>-0.342497</v>
       </c>
       <c r="T144" s="5" t="n">
         <v>-1.770476</v>

--- a/output/pdf_financials_xlsx/LITT.xlsx
+++ b/output/pdf_financials_xlsx/LITT.xlsx
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.07809199999999999</v>
+        <v>0.09729</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.11804</v>
+        <v>0.550357</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.726372</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.075776</v>
+        <v>-0.094974</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.495301</v>
+        <v>0.062984</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-2.050986</v>
@@ -1051,28 +1051,28 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.080758</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.015479</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00096</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007243</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.026931</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000822</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000182</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -2067,28 +2067,28 @@
         <v>0.062984</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.050986</v>
+        <v>-2.131744</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.296018</v>
+        <v>-1.311497</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.07595300000000001</v>
+        <v>-0.076913</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.8550680000000001</v>
+        <v>-0.862311</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.618045</v>
+        <v>-0.644976</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.597435</v>
+        <v>-0.598257</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.783552</v>
+        <v>-0.7835530000000001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.20251</v>
+        <v>-0.202692</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-4.161663</v>
@@ -2187,28 +2187,28 @@
         <v>0.062984</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.050664</v>
+        <v>-2.131422</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.295233</v>
+        <v>-1.310712</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.07135</v>
+        <v>-0.07231</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.849751</v>
+        <v>-0.856994</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.616752</v>
+        <v>-0.643683</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.596372</v>
+        <v>-0.597194</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.781593</v>
+        <v>-0.781594</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.200753</v>
+        <v>-0.200935</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-4.15943</v>
@@ -2247,28 +2247,28 @@
         <v>10.26900207225671</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>154.8121943449186</v>
+        <v>160.9089138420702</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>187.2598047932778</v>
+        <v>189.4976990705199</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-20.57636904229763</v>
+        <v>-20.85321997825567</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>396.3261460679922</v>
+        <v>399.7043006991376</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>556.5499878177536</v>
+        <v>580.852215815263</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-1337.126970247304</v>
+        <v>-1338.969978251609</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-764.6035100076305</v>
+        <v>-764.6044882706267</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-222.5593667546174</v>
+        <v>-222.7611361167158</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>203.1964842190934</v>
@@ -2460,19 +2460,19 @@
         <v>0.539295</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.308476</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.607491</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.140631</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.150746</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.049674</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.227251</v>
@@ -2481,22 +2481,22 @@
         <v>0.316534</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.081786</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.011407</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.11168</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.166696</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.178368</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.025513</v>
       </c>
     </row>
     <row r="35">
@@ -2576,19 +2576,19 @@
         <v>0.539295</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.308476</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1</v>
+        <v>0.707491</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.140631</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.150746</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.049674</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.227251</v>
@@ -2597,22 +2597,22 @@
         <v>0.316534</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.081786</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.011407</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.11168</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.166696</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.178368</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.025513</v>
       </c>
     </row>
     <row r="37">
@@ -3272,19 +3272,19 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.198704</v>
+        <v>0.890228</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.256298</v>
+        <v>0.648807</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.3911</v>
+        <v>0.250469</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.249704</v>
+        <v>0.098958</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.096818</v>
+        <v>0.047144</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.069523</v>
@@ -3293,22 +3293,22 @@
         <v>0.143404</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.235108</v>
+        <v>0.153322</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.753775</v>
+        <v>1.742368</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.50492</v>
+        <v>0.39324</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>7.198402</v>
+        <v>7.031706</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.518448</v>
+        <v>5.34008</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4.403697</v>
+        <v>4.378184</v>
       </c>
     </row>
     <row r="49">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -49439,7 +49439,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -51549,7 +51549,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -52571,7 +52571,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -54476,7 +54476,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -63294,7 +63294,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E551" s="5" t="n">
